--- a/docs/演示导入模板-合作项目.xlsx
+++ b/docs/演示导入模板-合作项目.xlsx
@@ -21,39 +21,41 @@
   <si>
     <t>填写说明：
 * 必填列。
-项目类型：文本，选填
+合作类型：文本，选填
 项目阶段：启动 / 执行中 / 验收 / 关闭（或 initiation / execution / acceptance / closure），默认为 启动
+预算：文本，选填
 开始日期 / 结束日期：格式 YYYY-MM-DD，选填
-关联合作企业：企业名称，选填，多值用中文分号「；」分隔，需与系统「合作企业」中的企业名称一致
-关联二级学院：学院名称，选填，多值用中文分号「；」分隔
+项目描述：文本，选填
+合作企业：企业名称，选填，多值用中文分号「；」分隔，需与系统「合作企业」中的企业名称一致（按名称自动关联）
+二级学院：学院名称，选填，多值用中文分号「；」分隔
 公开显示：是 / 否，选填，默认为 否</t>
   </si>
   <si>
     <t>项目名称 *</t>
   </si>
   <si>
-    <t>项目类型</t>
+    <t>合作类型</t>
   </si>
   <si>
     <t>项目阶段</t>
   </si>
   <si>
+    <t>预算</t>
+  </si>
+  <si>
     <t>开始日期</t>
   </si>
   <si>
     <t>结束日期</t>
   </si>
   <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <t>预算</t>
-  </si>
-  <si>
-    <t>关联合作企业</t>
-  </si>
-  <si>
-    <t>关联二级学院</t>
+    <t>项目描述</t>
+  </si>
+  <si>
+    <t>合作企业</t>
+  </si>
+  <si>
+    <t>二级学院</t>
   </si>
   <si>
     <t>公开显示</t>
@@ -68,6 +70,9 @@
     <t>执行中</t>
   </si>
   <si>
+    <t>300万</t>
+  </si>
+  <si>
     <t>2026-03-01</t>
   </si>
   <si>
@@ -77,9 +82,6 @@
     <t>校企共建新能源汽车充电桩技术研发平台，围绕充电效率、智能运维与安全防护开展联合攻关，共同培养新能源领域高技能人才。</t>
   </si>
   <si>
-    <t>300万</t>
-  </si>
-  <si>
     <t>南京云驰新能源科技有限公司</t>
   </si>
   <si>
@@ -98,6 +100,9 @@
     <t>启动</t>
   </si>
   <si>
+    <t>500万</t>
+  </si>
+  <si>
     <t>2026-06-01</t>
   </si>
   <si>
@@ -107,9 +112,6 @@
     <t>联合建设智能制造实训基地，导入企业真实产线与数字化制造系统，支撑机电类专业群实践教学与社会培训。</t>
   </si>
   <si>
-    <t>500万</t>
-  </si>
-  <si>
     <t>苏州华芯智能制造有限公司</t>
   </si>
   <si>
@@ -122,6 +124,9 @@
     <t>验收</t>
   </si>
   <si>
+    <t>120万</t>
+  </si>
+  <si>
     <t>2025-09-01</t>
   </si>
   <si>
@@ -129,9 +134,6 @@
   </si>
   <si>
     <t>基于企业智慧教育装备产品，校企共同开发配套实训课程与教学资源包，服务信息化教学改革。</t>
-  </si>
-  <si>
-    <t>120万</t>
   </si>
   <si>
     <t>无锡智联教育装备有限公司</t>
@@ -470,15 +472,15 @@
     <col customWidth="true" max="1" min="1" width="32"/>
     <col customWidth="true" max="2" min="2" width="20"/>
     <col customWidth="true" max="3" min="3" width="22"/>
-    <col customWidth="true" max="5" min="4" width="16"/>
-    <col customWidth="true" max="6" min="6" width="50"/>
-    <col customWidth="true" max="7" min="7" width="20"/>
+    <col customWidth="true" max="4" min="4" width="20"/>
+    <col customWidth="true" max="6" min="5" width="16"/>
+    <col customWidth="true" max="7" min="7" width="50"/>
     <col customWidth="true" max="8" min="8" width="44"/>
     <col customWidth="true" max="9" min="9" width="30"/>
     <col customWidth="true" max="10" min="10" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="240" customHeight="true">
+    <row r="1" ht="272" customHeight="true">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
